--- a/data/trans_camb/P2B_R-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P2B_R-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>38,79; 62,2</t>
+          <t>37,88; 61,75</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>26,29; 50,24</t>
+          <t>23,66; 49,9</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-16,81; 4,76</t>
+          <t>-17,78; 4,42</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>33,98; 55,67</t>
+          <t>32,21; 56,14</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>32,21; 56,77</t>
+          <t>32,26; 56,06</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-20,79; 4,4</t>
+          <t>-20,55; 3,57</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>39,04; 55,55</t>
+          <t>39,9; 55,52</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>32,97; 49,79</t>
+          <t>33,46; 50,63</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-14,26; 1,29</t>
+          <t>-14,71; 0,36</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>100,2; 265,11</t>
+          <t>104,43; 258,83</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>69,38; 209,78</t>
+          <t>65,29; 206,33</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-45,88; 21,41</t>
+          <t>-47,65; 18,88</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>78,99; 203,26</t>
+          <t>73,53; 198,92</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>76,34; 206,18</t>
+          <t>73,24; 195,28</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-47,81; 14,91</t>
+          <t>-47,06; 13,17</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>102,84; 204,46</t>
+          <t>106,52; 200,68</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>87,55; 177,91</t>
+          <t>88,7; 183,26</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-38,12; 4,65</t>
+          <t>-40,35; 1,37</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>28,65; 53,67</t>
+          <t>29,58; 55,44</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>27,29; 51,11</t>
+          <t>28,34; 51,48</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-14,8; 10,33</t>
+          <t>-14,24; 9,94</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>41,05; 63,55</t>
+          <t>39,82; 63,2</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>22,34; 46,54</t>
+          <t>21,6; 46,75</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-14,93; 9,41</t>
+          <t>-14,8; 8,46</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>38,64; 56,06</t>
+          <t>38,61; 55,21</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>28,1; 46,03</t>
+          <t>27,97; 46,45</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-9,59; 8,07</t>
+          <t>-10,66; 6,73</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>62,73; 187,77</t>
+          <t>68,32; 199,99</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>61,23; 175,94</t>
+          <t>63,43; 177,39</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-32,35; 38,62</t>
+          <t>-33,37; 32,94</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>103,46; 265,4</t>
+          <t>98,02; 261,76</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>55,46; 192,82</t>
+          <t>55,39; 188,94</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-37,66; 35,44</t>
+          <t>-36,86; 34,66</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,71; 197,92</t>
+          <t>93,66; 192,59</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>70,65; 162,33</t>
+          <t>72,43; 165,23</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-26,13; 26,32</t>
+          <t>-26,48; 22,78</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>42,59; 66,07</t>
+          <t>40,8; 66,16</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>26,03; 54,99</t>
+          <t>23,56; 53,12</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-8,79; 20,53</t>
+          <t>-10,29; 20,09</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>44,57; 66,01</t>
+          <t>44,06; 64,46</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>25,11; 50,24</t>
+          <t>23,33; 48,89</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-6,73; 21,64</t>
+          <t>-6,41; 20,5</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>47,18; 62,58</t>
+          <t>47,2; 62,84</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>29,11; 47,95</t>
+          <t>28,98; 47,16</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-3,02; 15,62</t>
+          <t>-3,24; 16,12</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>113,42; 332,74</t>
+          <t>112,03; 330,15</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>73,19; 271,1</t>
+          <t>66,63; 248,77</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-27,08; 97,08</t>
+          <t>-29,81; 91,28</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>125,75; 302,62</t>
+          <t>123,42; 303,65</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>72,88; 223,08</t>
+          <t>69,37; 221,82</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-20,19; 90,96</t>
+          <t>-18,93; 88,52</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>144,0; 274,2</t>
+          <t>140,67; 279,77</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>89,77; 200,4</t>
+          <t>89,84; 199,34</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-9,64; 64,82</t>
+          <t>-10,22; 63,74</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>44,61; 60,64</t>
+          <t>44,53; 60,23</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>31,45; 48,37</t>
+          <t>31,62; 47,94</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-13,88; 7,11</t>
+          <t>-13,62; 6,76</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>47,87; 62,7</t>
+          <t>48,63; 62,59</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>29,87; 46,69</t>
+          <t>29,58; 46,56</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-9,01; 6,95</t>
+          <t>-9,1; 8,15</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>48,58; 59,54</t>
+          <t>49,38; 59,68</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>32,83; 45,37</t>
+          <t>32,81; 44,59</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-9,15; 4,37</t>
+          <t>-9,4; 4,31</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>126,59; 245,14</t>
+          <t>127,08; 247,69</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>89,9; 193,66</t>
+          <t>92,06; 189,69</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-41,98; 27,37</t>
+          <t>-41,9; 25,08</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>132,66; 245,65</t>
+          <t>129,76; 239,02</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>84,1; 176,15</t>
+          <t>81,37; 176,31</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-25,65; 26,22</t>
+          <t>-25,81; 30,07</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>142,7; 223,26</t>
+          <t>143,74; 223,8</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>96,4; 166,95</t>
+          <t>94,49; 165,05</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-27,01; 15,48</t>
+          <t>-29,12; 15,27</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>39,07; 61,3</t>
+          <t>38,89; 60,66</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>16,89; 41,85</t>
+          <t>17,61; 41,71</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-14,3; 9,57</t>
+          <t>-13,54; 10,62</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>36,05; 57,74</t>
+          <t>35,29; 57,64</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>28,12; 50,16</t>
+          <t>27,94; 50,88</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-3,22; 23,19</t>
+          <t>-2,76; 22,95</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>41,5; 56,54</t>
+          <t>40,25; 57,1</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>26,24; 42,19</t>
+          <t>26,07; 42,51</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-3,64; 14,39</t>
+          <t>-3,34; 15,02</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>87,73; 221,74</t>
+          <t>89,07; 223,21</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>39,3; 150,48</t>
+          <t>39,71; 153,35</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-32,86; 33,04</t>
+          <t>-31,25; 37,64</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>87,13; 226,48</t>
+          <t>86,7; 226,49</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>70,38; 190,24</t>
+          <t>69,87; 196,77</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-8,8; 87,23</t>
+          <t>-8,96; 83,31</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>103,45; 197,46</t>
+          <t>104,01; 202,25</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>66,08; 143,32</t>
+          <t>67,02; 147,07</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-9,39; 49,06</t>
+          <t>-9,27; 49,56</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>33,93; 59,67</t>
+          <t>35,77; 59,92</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>11,28; 38,18</t>
+          <t>12,9; 40,35</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-3,39; 23,8</t>
+          <t>-3,39; 23,44</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>50,27; 70,86</t>
+          <t>50,35; 71,87</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>24,75; 51,61</t>
+          <t>25,55; 52,18</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>15,07; 42,16</t>
+          <t>16,05; 41,84</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>46,1; 62,36</t>
+          <t>46,59; 62,84</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>22,91; 41,01</t>
+          <t>22,27; 41,65</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>8,92; 27,77</t>
+          <t>10,28; 28,73</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>89,28; 252,02</t>
+          <t>89,6; 245,84</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>29,54; 155,58</t>
+          <t>36,14; 160,28</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-9,04; 94,24</t>
+          <t>-10,02; 91,12</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>176,14; 500,25</t>
+          <t>178,88; 519,96</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>91,05; 346,52</t>
+          <t>94,93; 347,54</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>57,91; 284,7</t>
+          <t>59,4; 278,82</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>144,8; 296,17</t>
+          <t>147,78; 295,96</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>72,56; 190,03</t>
+          <t>71,96; 190,44</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>30,01; 127,24</t>
+          <t>32,96; 128,95</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>46,75; 55,57</t>
+          <t>46,48; 54,95</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>31,72; 41,31</t>
+          <t>31,53; 41,13</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-6,81; 3,88</t>
+          <t>-6,65; 3,84</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>49,08; 57,45</t>
+          <t>49,13; 57,4</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>34,92; 43,63</t>
+          <t>34,65; 44,41</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-0,04; 9,59</t>
+          <t>-0,53; 8,85</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>49,11; 55,26</t>
+          <t>49,07; 55,09</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>34,67; 41,01</t>
+          <t>34,58; 41,19</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 5,57</t>
+          <t>-2,05; 5,47</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>134,25; 193,28</t>
+          <t>136,17; 192,18</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>91,4; 143,23</t>
+          <t>92,26; 143,6</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-19,98; 13,16</t>
+          <t>-19,41; 12,66</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>147,77; 211,5</t>
+          <t>148,12; 210,16</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>106,0; 157,41</t>
+          <t>105,19; 163,81</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 34,91</t>
+          <t>-1,73; 30,69</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>149,16; 191,47</t>
+          <t>149,1; 189,65</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>106,15; 143,39</t>
+          <t>104,62; 141,52</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-4,58; 18,71</t>
+          <t>-6,32; 18,61</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2B_R-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P2B_R-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>37,88; 61,75</t>
+          <t>38,43; 61,41</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>23,66; 49,9</t>
+          <t>24,38; 49,83</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-17,78; 4,42</t>
+          <t>-16,72; 4,18</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>32,21; 56,14</t>
+          <t>31,83; 55,92</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>32,26; 56,06</t>
+          <t>32,32; 55,73</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-20,55; 3,57</t>
+          <t>-20,0; 3,14</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>39,9; 55,52</t>
+          <t>39,74; 56,39</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>33,46; 50,63</t>
+          <t>33,65; 50,45</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-14,71; 0,36</t>
+          <t>-14,41; 1,08</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>104,43; 258,83</t>
+          <t>102,61; 262,51</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>65,29; 206,33</t>
+          <t>65,45; 219,47</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-47,65; 18,88</t>
+          <t>-46,78; 16,91</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>73,53; 198,92</t>
+          <t>74,63; 206,89</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>73,24; 195,28</t>
+          <t>74,74; 205,2</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-47,06; 13,17</t>
+          <t>-48,1; 11,8</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>106,52; 200,68</t>
+          <t>104,08; 204,77</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>88,7; 183,26</t>
+          <t>87,51; 185,53</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-40,35; 1,37</t>
+          <t>-39,08; 4,49</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>29,58; 55,44</t>
+          <t>29,06; 54,26</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>28,34; 51,48</t>
+          <t>29,65; 52,16</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-14,24; 9,94</t>
+          <t>-14,39; 10,68</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>39,82; 63,2</t>
+          <t>39,67; 62,51</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>21,6; 46,75</t>
+          <t>22,02; 45,91</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-14,8; 8,46</t>
+          <t>-14,32; 10,45</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>38,61; 55,21</t>
+          <t>38,52; 55,0</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>27,97; 46,45</t>
+          <t>28,61; 45,89</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-10,66; 6,73</t>
+          <t>-10,27; 7,18</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>68,32; 199,99</t>
+          <t>65,38; 185,59</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>63,43; 177,39</t>
+          <t>68,84; 191,21</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-33,37; 32,94</t>
+          <t>-33,04; 37,04</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>98,02; 261,76</t>
+          <t>94,23; 248,99</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>55,39; 188,94</t>
+          <t>52,27; 177,63</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-36,86; 34,66</t>
+          <t>-38,64; 42,42</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,66; 192,59</t>
+          <t>98,81; 196,83</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>72,43; 165,23</t>
+          <t>71,78; 158,26</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-26,48; 22,78</t>
+          <t>-26,47; 24,12</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>40,8; 66,16</t>
+          <t>41,79; 66,73</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>23,56; 53,12</t>
+          <t>23,52; 53,12</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-10,29; 20,09</t>
+          <t>-9,48; 20,56</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>44,06; 64,46</t>
+          <t>43,61; 65,78</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>23,33; 48,89</t>
+          <t>23,77; 50,19</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-6,41; 20,5</t>
+          <t>-6,76; 20,97</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>47,2; 62,84</t>
+          <t>47,28; 62,8</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>28,98; 47,16</t>
+          <t>28,53; 47,74</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-3,24; 16,12</t>
+          <t>-4,67; 15,14</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>112,03; 330,15</t>
+          <t>113,25; 333,89</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>66,63; 248,77</t>
+          <t>66,68; 258,66</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-29,81; 91,28</t>
+          <t>-29,17; 94,44</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>123,42; 303,65</t>
+          <t>121,22; 314,45</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>69,37; 221,82</t>
+          <t>67,59; 236,78</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-18,93; 88,52</t>
+          <t>-19,5; 91,96</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>140,67; 279,77</t>
+          <t>140,36; 275,11</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>89,84; 199,34</t>
+          <t>89,08; 204,0</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-10,22; 63,74</t>
+          <t>-15,62; 61,56</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>44,53; 60,23</t>
+          <t>44,08; 61,02</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>31,62; 47,94</t>
+          <t>31,44; 47,58</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-13,62; 6,76</t>
+          <t>-14,77; 6,1</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>48,63; 62,59</t>
+          <t>47,67; 63,22</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>29,58; 46,56</t>
+          <t>30,18; 47,57</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-9,1; 8,15</t>
+          <t>-9,57; 8,02</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>49,38; 59,68</t>
+          <t>49,49; 59,87</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>32,81; 44,59</t>
+          <t>33,09; 45,34</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-9,4; 4,31</t>
+          <t>-9,81; 4,23</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>127,08; 247,69</t>
+          <t>127,35; 245,98</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>92,06; 189,69</t>
+          <t>88,14; 192,99</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-41,9; 25,08</t>
+          <t>-44,32; 23,37</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>129,76; 239,02</t>
+          <t>129,94; 249,85</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>81,37; 176,31</t>
+          <t>85,35; 190,95</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-25,81; 30,07</t>
+          <t>-27,32; 30,31</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>143,74; 223,8</t>
+          <t>145,5; 227,5</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>94,49; 165,05</t>
+          <t>97,67; 167,3</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-29,12; 15,27</t>
+          <t>-29,71; 15,02</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>38,89; 60,66</t>
+          <t>40,05; 61,01</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>17,61; 41,71</t>
+          <t>18,41; 42,6</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-13,54; 10,62</t>
+          <t>-12,97; 9,66</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>35,29; 57,64</t>
+          <t>37,5; 58,49</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>27,94; 50,88</t>
+          <t>27,83; 50,89</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-2,76; 22,95</t>
+          <t>-2,33; 24,1</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>40,25; 57,1</t>
+          <t>41,64; 56,86</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>26,07; 42,51</t>
+          <t>25,93; 42,28</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-3,34; 15,02</t>
+          <t>-4,64; 13,22</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>89,07; 223,21</t>
+          <t>89,07; 224,85</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>39,71; 153,35</t>
+          <t>41,73; 153,22</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-31,25; 37,64</t>
+          <t>-31,57; 35,22</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>86,7; 226,49</t>
+          <t>93,28; 230,14</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>69,87; 196,77</t>
+          <t>68,03; 191,91</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-8,96; 83,31</t>
+          <t>-7,61; 83,7</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>104,01; 202,25</t>
+          <t>106,8; 199,09</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>67,02; 147,07</t>
+          <t>65,16; 145,31</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-9,27; 49,56</t>
+          <t>-12,31; 42,88</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>35,77; 59,92</t>
+          <t>35,52; 60,03</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>12,9; 40,35</t>
+          <t>11,26; 39,72</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-3,39; 23,44</t>
+          <t>-3,7; 23,39</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>50,35; 71,87</t>
+          <t>50,78; 71,14</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>25,55; 52,18</t>
+          <t>26,08; 51,09</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>16,05; 41,84</t>
+          <t>15,51; 41,92</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>46,59; 62,84</t>
+          <t>46,94; 61,88</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>22,27; 41,65</t>
+          <t>24,23; 41,24</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>10,28; 28,73</t>
+          <t>9,15; 28,54</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>89,6; 245,84</t>
+          <t>94,37; 248,11</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>36,14; 160,28</t>
+          <t>29,31; 159,84</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-10,02; 91,12</t>
+          <t>-10,45; 91,7</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>178,88; 519,96</t>
+          <t>182,49; 500,39</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>94,93; 347,54</t>
+          <t>93,7; 341,65</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>59,4; 278,82</t>
+          <t>54,53; 291,42</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>147,78; 295,96</t>
+          <t>151,0; 296,96</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>71,96; 190,44</t>
+          <t>78,6; 193,73</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>32,96; 128,95</t>
+          <t>29,32; 125,56</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>46,48; 54,95</t>
+          <t>46,42; 55,58</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>31,53; 41,13</t>
+          <t>31,63; 41,3</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-6,65; 3,84</t>
+          <t>-6,69; 4,18</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>49,13; 57,4</t>
+          <t>49,34; 57,06</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>34,65; 44,41</t>
+          <t>34,74; 43,53</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 8,85</t>
+          <t>-0,53; 8,87</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>49,07; 55,09</t>
+          <t>49,33; 55,37</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>34,58; 41,19</t>
+          <t>35,02; 41,62</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-2,05; 5,47</t>
+          <t>-1,84; 5,72</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>136,17; 192,18</t>
+          <t>132,25; 192,45</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>92,26; 143,6</t>
+          <t>92,17; 143,65</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-19,41; 12,66</t>
+          <t>-19,84; 13,99</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>148,12; 210,16</t>
+          <t>148,16; 208,35</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>105,19; 163,81</t>
+          <t>106,05; 155,38</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 30,69</t>
+          <t>-2,27; 31,69</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>149,1; 189,65</t>
+          <t>150,01; 192,88</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>104,62; 141,52</t>
+          <t>107,19; 145,18</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-6,32; 18,61</t>
+          <t>-5,58; 19,35</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2B_R-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P2B_R-Clase-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>45,12</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>45,43</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-6,03</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>51,36</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>37,83</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-6,34</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>45,12</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>45,43</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-8,11</t>
+          <t>-5,94</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-6,87</t>
+          <t>-5,63</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>38,43; 61,41</t>
+          <t>33,98; 55,67</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>24,38; 49,83</t>
+          <t>32,21; 56,77</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-16,72; 4,18</t>
+          <t>-17,77; 6,35</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>31,83; 55,92</t>
+          <t>38,79; 62,2</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>32,32; 55,73</t>
+          <t>26,29; 50,24</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-20,0; 3,14</t>
+          <t>-16,89; 5,17</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>39,74; 56,39</t>
+          <t>39,04; 55,55</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>33,65; 50,45</t>
+          <t>32,97; 49,79</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-14,41; 1,08</t>
+          <t>-13,15; 2,32</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>127,69%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>128,55%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-17,05%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>168,93%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>124,41%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-20,84%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>127,69%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>128,55%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-22,95%</t>
+          <t>-19,53%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-20,99%</t>
+          <t>-17,21%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>102,61; 262,51</t>
+          <t>78,99; 203,26</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>65,45; 219,47</t>
+          <t>76,34; 206,18</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-46,78; 16,91</t>
+          <t>-43,12; 21,99</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>74,63; 206,89</t>
+          <t>100,2; 265,11</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>74,74; 205,2</t>
+          <t>69,38; 209,78</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-48,1; 11,8</t>
+          <t>-44,94; 22,78</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>104,08; 204,77</t>
+          <t>102,84; 204,46</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>87,51; 185,53</t>
+          <t>87,55; 177,91</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-39,08; 4,49</t>
+          <t>-35,63; 8,35</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>52,32</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>34,78</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>-1,05</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>42,58</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>40,41</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-1,71</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>52,32</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>34,78</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-1,83</t>
+          <t>-0,99</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-1,79</t>
+          <t>-0,98</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>29,06; 54,26</t>
+          <t>41,05; 63,55</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>29,65; 52,16</t>
+          <t>22,34; 46,54</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-14,39; 10,68</t>
+          <t>-14,25; 10,37</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>39,67; 62,51</t>
+          <t>28,65; 53,67</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>22,02; 45,91</t>
+          <t>27,29; 51,11</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-14,32; 10,45</t>
+          <t>-13,92; 11,07</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>38,52; 55,0</t>
+          <t>38,64; 56,06</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>28,61; 45,89</t>
+          <t>28,1; 46,03</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-10,27; 7,18</t>
+          <t>-8,88; 8,75</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>163,89%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>108,95%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>-3,28%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>119,06%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>113,02%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-4,78%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>163,89%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>108,95%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-5,72%</t>
+          <t>-2,77%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-5,3%</t>
+          <t>-2,9%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>65,38; 185,59</t>
+          <t>103,46; 265,4</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>68,84; 191,21</t>
+          <t>55,46; 192,82</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-33,04; 37,04</t>
+          <t>-36,62; 37,96</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>94,23; 248,99</t>
+          <t>62,73; 187,77</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>52,27; 177,63</t>
+          <t>61,23; 175,94</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-38,64; 42,42</t>
+          <t>-31,32; 41,49</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,81; 196,83</t>
+          <t>95,71; 197,92</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>71,78; 158,26</t>
+          <t>70,65; 162,33</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-26,47; 24,12</t>
+          <t>-23,6; 29,02</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>55,02</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>37,19</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>7,82</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>55,34</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>40,35</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>5,15</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>55,02</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>37,19</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7,0</t>
+          <t>6,45</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>6,16</t>
+          <t>7,14</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>41,79; 66,73</t>
+          <t>44,57; 66,01</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>23,52; 53,12</t>
+          <t>25,11; 50,24</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-9,48; 20,56</t>
+          <t>-5,63; 22,58</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>43,61; 65,78</t>
+          <t>42,59; 66,07</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>23,77; 50,19</t>
+          <t>26,03; 54,99</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-6,76; 20,97</t>
+          <t>-7,95; 22,55</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>47,28; 62,8</t>
+          <t>47,18; 62,58</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>28,53; 47,74</t>
+          <t>29,11; 47,95</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-4,67; 15,14</t>
+          <t>-2,65; 17,44</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>192,86%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>130,36%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>27,43%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>195,85%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>142,8%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>18,23%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>192,86%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>130,36%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>22,84%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>25,13%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>113,25; 333,89</t>
+          <t>125,75; 302,62</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>66,68; 258,66</t>
+          <t>72,88; 223,08</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-29,17; 94,44</t>
+          <t>-17,62; 100,69</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>121,22; 314,45</t>
+          <t>113,42; 332,74</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>67,59; 236,78</t>
+          <t>73,19; 271,1</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-19,5; 91,96</t>
+          <t>-24,81; 103,76</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>140,36; 275,11</t>
+          <t>144,0; 274,2</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>89,08; 204,0</t>
+          <t>89,77; 200,4</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-15,62; 61,56</t>
+          <t>-8,51; 69,79</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>55,64</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>38,66</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-0,8</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>53,05</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>40,23</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-3,19</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>55,64</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>38,66</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-1,11</t>
+          <t>-1,21</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-2,14</t>
+          <t>-0,93</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>44,08; 61,02</t>
+          <t>47,87; 62,7</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>31,44; 47,58</t>
+          <t>29,87; 46,69</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-14,77; 6,1</t>
+          <t>-8,95; 7,49</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>47,67; 63,22</t>
+          <t>44,61; 60,64</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>30,18; 47,57</t>
+          <t>31,45; 48,37</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-9,57; 8,02</t>
+          <t>-9,38; 7,14</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>49,49; 59,87</t>
+          <t>48,58; 59,54</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>33,09; 45,34</t>
+          <t>32,83; 45,37</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-9,81; 4,23</t>
+          <t>-6,63; 4,92</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>177,81%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>123,56%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-2,55%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>179,27%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>135,95%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-10,77%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>177,81%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>123,56%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-3,56%</t>
+          <t>-4,08%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-7,04%</t>
+          <t>-3,06%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>127,35; 245,98</t>
+          <t>132,66; 245,65</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>88,14; 192,99</t>
+          <t>84,1; 176,15</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-44,32; 23,37</t>
+          <t>-24,95; 28,34</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>129,94; 249,85</t>
+          <t>126,59; 245,14</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>85,35; 190,95</t>
+          <t>89,9; 193,66</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-27,32; 30,31</t>
+          <t>-27,94; 27,31</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>145,5; 227,5</t>
+          <t>142,7; 223,26</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>97,67; 167,3</t>
+          <t>96,4; 166,95</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-29,71; 15,02</t>
+          <t>-19,93; 17,09</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>47,82</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>39,54</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>9,76</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>51,07</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>29,91</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-1,36</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>47,82</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>39,54</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>9,22</t>
+          <t>0,27</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>4,67</t>
+          <t>5,52</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>40,05; 61,01</t>
+          <t>36,05; 57,74</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>18,41; 42,6</t>
+          <t>28,12; 50,16</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-12,97; 9,66</t>
+          <t>-2,2; 22,89</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>37,5; 58,49</t>
+          <t>39,07; 61,3</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>27,83; 50,89</t>
+          <t>16,89; 41,85</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 24,1</t>
+          <t>-13,07; 11,14</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>41,64; 56,86</t>
+          <t>41,5; 56,54</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>25,93; 42,28</t>
+          <t>26,24; 42,19</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-4,64; 13,22</t>
+          <t>-2,42; 14,66</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>145,35%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>120,18%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>29,66%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>143,46%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>84,01%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-3,81%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>145,35%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>120,18%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>28,01%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>16,19%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>89,07; 224,85</t>
+          <t>87,13; 226,48</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>41,73; 153,22</t>
+          <t>70,38; 190,24</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-31,57; 35,22</t>
+          <t>-6,15; 87,69</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>93,28; 230,14</t>
+          <t>87,73; 221,74</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>68,03; 191,91</t>
+          <t>39,3; 150,48</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-7,61; 83,7</t>
+          <t>-30,29; 40,03</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>106,8; 199,09</t>
+          <t>103,45; 197,46</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>65,16; 145,31</t>
+          <t>66,08; 143,32</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-12,31; 42,88</t>
+          <t>-7,2; 50,18</t>
         </is>
       </c>
     </row>
@@ -1704,32 +1704,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>61,43</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>39,17</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>30,97</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t>48,57</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>25,71</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>9,9</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>61,43</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>39,17</t>
-        </is>
-      </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>28,39</t>
+          <t>8,37</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>19,14</t>
+          <t>19,49</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>35,52; 60,03</t>
+          <t>50,27; 70,86</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>11,26; 39,72</t>
+          <t>24,75; 51,61</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-3,7; 23,39</t>
+          <t>17,41; 44,75</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>50,78; 71,14</t>
+          <t>33,93; 59,67</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>26,08; 51,09</t>
+          <t>11,28; 38,18</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>15,51; 41,92</t>
+          <t>-5,19; 21,44</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>46,94; 61,88</t>
+          <t>46,1; 62,36</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>24,23; 41,24</t>
+          <t>22,91; 41,01</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>9,15; 28,54</t>
+          <t>9,12; 28,26</t>
         </is>
       </c>
     </row>
@@ -1810,32 +1810,32 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>297,78%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>189,86%</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>150,13%</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>154,39%</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>81,72%</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>31,46%</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>297,78%</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>189,86%</t>
-        </is>
-      </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>137,62%</t>
+          <t>26,6%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>73,22%</t>
+          <t>74,57%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>94,37; 248,11</t>
+          <t>176,14; 500,25</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>29,31; 159,84</t>
+          <t>91,05; 346,52</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-10,45; 91,7</t>
+          <t>65,56; 299,23</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>182,49; 500,39</t>
+          <t>89,28; 252,02</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>93,7; 341,65</t>
+          <t>29,54; 155,58</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>54,53; 291,42</t>
+          <t>-13,41; 83,62</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>151,0; 296,96</t>
+          <t>144,8; 296,17</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>78,6; 193,73</t>
+          <t>72,56; 190,03</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>29,32; 125,56</t>
+          <t>30,64; 130,51</t>
         </is>
       </c>
     </row>
@@ -1920,32 +1920,32 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>53,26</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>39,4</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>5,26</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>51,05</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>36,67</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>-0,83</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>53,26</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>39,4</t>
-        </is>
-      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,23</t>
+          <t>0,49</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>1,84</t>
+          <t>2,98</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>46,42; 55,58</t>
+          <t>49,08; 57,45</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>31,63; 41,3</t>
+          <t>34,92; 43,63</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-6,69; 4,18</t>
+          <t>0,98; 10,79</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>49,34; 57,06</t>
+          <t>46,75; 55,57</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>34,74; 43,53</t>
+          <t>31,72; 41,31</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 8,87</t>
+          <t>-4,87; 4,82</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>49,33; 55,37</t>
+          <t>49,11; 55,26</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>35,02; 41,62</t>
+          <t>34,67; 41,01</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 5,72</t>
+          <t>-0,09; 6,51</t>
         </is>
       </c>
     </row>
@@ -2026,32 +2026,32 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>175,9%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>130,13%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>17,39%</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>162,0%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>116,36%</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>-2,64%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>175,9%</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>130,13%</t>
-        </is>
-      </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>9,66%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>132,25; 192,45</t>
+          <t>147,77; 211,5</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>92,17; 143,65</t>
+          <t>106,0; 157,41</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-19,84; 13,99</t>
+          <t>2,72; 39,2</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>148,16; 208,35</t>
+          <t>134,25; 193,28</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>106,05; 155,38</t>
+          <t>91,4; 143,23</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 31,69</t>
+          <t>-13,87; 16,38</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>150,01; 192,88</t>
+          <t>149,16; 191,47</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>107,19; 145,18</t>
+          <t>106,15; 143,39</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-5,58; 19,35</t>
+          <t>-0,29; 22,04</t>
         </is>
       </c>
     </row>
